--- a/src/test/resources/meas.xlsx
+++ b/src/test/resources/meas.xlsx
@@ -1,31 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\comag\Documents\Projects\shopeesalescoverter\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A541E976-5ED8-43A2-98A3-767FDBEF9E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5B9D34-AD31-4475-B5A5-CF9CE66F74C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="86">
   <si>
     <t>Relative Key</t>
   </si>
@@ -39,6 +47,9 @@
     <t>Update Rule</t>
   </si>
   <si>
+    <t>relative product name</t>
+  </si>
+  <si>
     <t>2t</t>
   </si>
   <si>
@@ -52,19 +63,253 @@
   </si>
   <si>
     <t>mug</t>
+  </si>
+  <si>
+    <t>014-b</t>
+  </si>
+  <si>
+    <t>021-c</t>
+  </si>
+  <si>
+    <t>021-f</t>
+  </si>
+  <si>
+    <t>757</t>
+  </si>
+  <si>
+    <t>776-d</t>
+  </si>
+  <si>
+    <t>776-i</t>
+  </si>
+  <si>
+    <t>776-r</t>
+  </si>
+  <si>
+    <t>527-d</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>323-b</t>
+  </si>
+  <si>
+    <t>323-e</t>
+  </si>
+  <si>
+    <t>323-f</t>
+  </si>
+  <si>
+    <t>630-a</t>
+  </si>
+  <si>
+    <t>323-a</t>
+  </si>
+  <si>
+    <t>323-c</t>
+  </si>
+  <si>
+    <t>323-d</t>
+  </si>
+  <si>
+    <t>495</t>
+  </si>
+  <si>
+    <t>492</t>
+  </si>
+  <si>
+    <t>087-b</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>397</t>
+  </si>
+  <si>
+    <t>776-e</t>
+  </si>
+  <si>
+    <t>660-a</t>
+  </si>
+  <si>
+    <t>805</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>Chip Bulk Potato</t>
+  </si>
+  <si>
+    <t>Crunch Roll Vanilla</t>
+  </si>
+  <si>
+    <t>Chip Bulk Green Pea</t>
+  </si>
+  <si>
+    <t>Checkers Classic</t>
+  </si>
+  <si>
+    <t>Cookies Creeam 20pcs</t>
+  </si>
+  <si>
+    <t>Peanut Coated Chocolate 100pcs</t>
+  </si>
+  <si>
+    <t>Dried Fruit 2kg</t>
+  </si>
+  <si>
+    <t>Instant Powder Grape</t>
+  </si>
+  <si>
+    <t>Instant Powder Blueberry</t>
+  </si>
+  <si>
+    <t>Instant Powder Strawberry</t>
+  </si>
+  <si>
+    <t>Instant Powder Mango</t>
+  </si>
+  <si>
+    <t>Instant Powder Blackcurrant</t>
+  </si>
+  <si>
+    <t>Instant Powder Blackberry</t>
+  </si>
+  <si>
+    <t>Chocolate Bean 50pcs</t>
+  </si>
+  <si>
+    <t>Bubble Water Mini</t>
+  </si>
+  <si>
+    <t>Peanut Candy 1kg</t>
+  </si>
+  <si>
+    <t>Jelly Grab Shape 50pcs</t>
+  </si>
+  <si>
+    <t>Thai Snack Pop Can</t>
+  </si>
+  <si>
+    <t>Powder Fruit Candy</t>
+  </si>
+  <si>
+    <t>Jelly Cat Paw Shape</t>
+  </si>
+  <si>
+    <t>Gumm Bulk Egg</t>
+  </si>
+  <si>
+    <t>Gummy Bulk Teeth</t>
+  </si>
+  <si>
+    <t>Gummy Bulk Dolphin</t>
+  </si>
+  <si>
+    <t>Gummy Bulk Ice Cream</t>
+  </si>
+  <si>
+    <t>Whistle</t>
+  </si>
+  <si>
+    <t>782</t>
+  </si>
+  <si>
+    <t>515-a</t>
+  </si>
+  <si>
+    <t>515-b</t>
+  </si>
+  <si>
+    <t>515-c</t>
+  </si>
+  <si>
+    <t>515-e</t>
+  </si>
+  <si>
+    <t>094-b</t>
+  </si>
+  <si>
+    <t>094-a</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>296</t>
+  </si>
+  <si>
+    <t>513-a</t>
+  </si>
+  <si>
+    <t>014-a</t>
+  </si>
+  <si>
+    <t>794-e</t>
+  </si>
+  <si>
+    <t>094-c</t>
+  </si>
+  <si>
+    <t>Crunch Roll Chocolate</t>
+  </si>
+  <si>
+    <t>Keropok Cheese</t>
+  </si>
+  <si>
+    <t>Keropok BBQ</t>
+  </si>
+  <si>
+    <t>Keropok Spicy</t>
+  </si>
+  <si>
+    <t>Chocolate Classic</t>
+  </si>
+  <si>
+    <t>Sour Plum</t>
+  </si>
+  <si>
+    <t>Nougat Cocoa</t>
+  </si>
+  <si>
+    <t>Nougat Strawberry</t>
+  </si>
+  <si>
+    <t>Nougat Blueberry</t>
+  </si>
+  <si>
+    <t>Nougat Mango</t>
+  </si>
+  <si>
+    <t>Kacang Tumbuk</t>
+  </si>
+  <si>
+    <t>Sour Candy Blueberry</t>
+  </si>
+  <si>
+    <t>Lollipop 200pcs Classic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -75,7 +320,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -87,14 +339,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -141,20 +399,20 @@
         <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -184,12 +442,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -228,230 +486,909 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="37" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>123</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>9557203</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
         <v>124</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>9557204</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>125</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>9557205</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>126</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>9557206</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2">
+        <v>9557207</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2">
+        <v>9557208</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2">
+        <v>9557209</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="2">
+        <v>9557210</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2">
+        <v>9557211</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2">
+        <v>9557212</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="2">
+        <v>9557213</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2">
+        <v>9557214</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="2">
+        <v>9557215</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="2">
+        <v>9557216</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2">
+        <v>9557217</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="2">
+        <v>9557218</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="2">
+        <v>9557219</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="2">
+        <v>9557220</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="2">
+        <v>9557221</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="2">
+        <v>9557222</v>
+      </c>
+      <c r="C21" s="2">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="2">
+        <v>9557223</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>9557224</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="2">
+        <v>9557225</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="2">
+        <v>9557226</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="2">
+        <v>9557227</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="2">
+        <v>9557228</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="2">
+        <v>9557229</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="2">
+        <v>9557230</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="2">
+        <v>9557231</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="2">
+        <v>9557232</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1</v>
+      </c>
+      <c r="D31" t="s">
+        <v>5</v>
+      </c>
+      <c r="E31" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="2">
+        <v>9557233</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+      <c r="D32" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="2">
+        <v>9557234</v>
+      </c>
+      <c r="C33" s="2">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="2">
+        <v>9557235</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1</v>
+      </c>
+      <c r="D34" t="s">
+        <v>5</v>
+      </c>
+      <c r="E34" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="2">
+        <v>9557236</v>
+      </c>
+      <c r="C35" s="2">
+        <v>1</v>
+      </c>
+      <c r="D35" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="2">
+        <v>9557237</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1</v>
+      </c>
+      <c r="D36" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" s="2">
+        <v>9557238</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1</v>
+      </c>
+      <c r="D37" t="s">
+        <v>5</v>
+      </c>
+      <c r="E37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="2">
+        <v>9557239</v>
+      </c>
+      <c r="C38" s="2">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>5</v>
+      </c>
+      <c r="E38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="2">
+        <v>9557240</v>
+      </c>
+      <c r="C39" s="2">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" s="2">
+        <v>9557241</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1</v>
+      </c>
+      <c r="D40" t="s">
+        <v>5</v>
+      </c>
+      <c r="E40" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="2">
+        <v>9557242</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+      <c r="D41" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B42" s="2">
+        <v>9557243</v>
+      </c>
+      <c r="C42" s="2">
+        <v>1</v>
+      </c>
+      <c r="D42" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="2">
+        <v>9557244</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
